--- a/SGC-CKN/Excel/81a8fe97-52dd-4ab7-962e-f4df64682c98_Lô_CT-02_P1-114_D800_29-03-2026.xlsx
+++ b/SGC-CKN/Excel/81a8fe97-52dd-4ab7-962e-f4df64682c98_Lô_CT-02_P1-114_D800_29-03-2026.xlsx
@@ -112,20 +112,16 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">10:02
-29/03/2026</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
-  </si>
-  <si>
     <t xml:space="preserve">10:00
 29/03/2026</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+  </si>
+  <si>
     <t xml:space="preserve">10:40
 29/03/2026</t>
   </si>
@@ -166,22 +162,24 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt (chạm sỏi)</t>
   </si>
   <si>
-    <t xml:space="preserve">13:57
-29/03/2026</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">14:37
 29/03/2026</t>
   </si>
   <si>
+    <t>Chạm sỏi CĐ: -34,64</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+  </si>
+  <si>
     <t xml:space="preserve">16:08
 29/03/2026</t>
+  </si>
+  <si>
+    <t>Kết thúc khoan</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -218,7 +216,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -279,12 +277,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF7C2D12"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -307,7 +299,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -366,7 +358,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -377,11 +369,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -477,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -548,37 +535,34 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1205,13 +1189,13 @@
         <v>-4.3</v>
       </c>
       <c r="H12" s="9">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="I12" s="9">
         <v>2.8</v>
       </c>
       <c r="J12" s="8">
-        <v>7.64</v>
+        <v>8.4</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
@@ -1228,10 +1212,10 @@
         <v>34</v>
       </c>
       <c r="D13" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>35</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="12">
         <v>-4.3</v>
@@ -1254,19 +1238,19 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>39</v>
       </c>
       <c r="F14" s="15">
         <v>-7.8</v>
@@ -1289,19 +1273,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>41</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="18">
         <v>-16.6</v>
@@ -1324,22 +1308,22 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>45</v>
-      </c>
       <c r="F16" s="21">
-        <v>-24.8</v>
+        <v>-21.8</v>
       </c>
       <c r="G16" s="21">
         <v>-25.7</v>
@@ -1348,10 +1332,10 @@
         <v>2</v>
       </c>
       <c r="I16" s="21">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J16" s="24">
-        <v>0.45</v>
+        <v>1.95</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>29</v>
@@ -1359,19 +1343,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>47</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>48</v>
       </c>
       <c r="F17" s="25">
         <v>-25.7</v>
@@ -1380,16 +1364,16 @@
         <v>-38.5</v>
       </c>
       <c r="H17" s="25">
-        <v>0.28</v>
+        <v>0.95</v>
       </c>
       <c r="I17" s="25">
         <v>12.8</v>
       </c>
       <c r="J17" s="8">
-        <v>45.18</v>
+        <v>13.47</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1403,10 +1387,10 @@
         <v>50</v>
       </c>
       <c r="D18" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>51</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-38.5</v>
@@ -1420,27 +1404,27 @@
       <c r="I18" s="28">
         <v>5.86</v>
       </c>
-      <c r="J18" s="31">
+      <c r="J18" s="24">
         <v>3.86</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1611,13 +1595,13 @@
         <v>-4.3</v>
       </c>
       <c r="G3" s="9">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="H3" s="9">
         <v>2.8</v>
       </c>
       <c r="I3" s="8">
-        <v>7.64</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1657,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1686,7 +1670,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1715,13 +1699,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="21">
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-24.8</v>
+        <v>-21.8</v>
       </c>
       <c r="F7" s="21">
         <v>-25.7</v>
@@ -1730,10 +1714,10 @@
         <v>2</v>
       </c>
       <c r="H7" s="21">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="I7" s="24">
-        <v>0.45</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1744,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1756,13 +1740,13 @@
         <v>-38.5</v>
       </c>
       <c r="G8" s="25">
-        <v>0.28</v>
+        <v>0.95</v>
       </c>
       <c r="H8" s="25">
         <v>12.8</v>
       </c>
       <c r="I8" s="8">
-        <v>45.18</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1790,37 +1774,37 @@
       <c r="H9" s="28">
         <v>5.86</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="24">
         <v>3.86</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>-44.36</v>
       </c>
-      <c r="G10" s="34">
-        <v>6</v>
-      </c>
-      <c r="H10" s="34">
-        <v>44.36</v>
-      </c>
-      <c r="I10" s="34">
-        <v>7.39</v>
+      <c r="G10" s="33">
+        <v>6.63</v>
+      </c>
+      <c r="H10" s="33">
+        <v>47.36</v>
+      </c>
+      <c r="I10" s="33">
+        <v>7.14</v>
       </c>
     </row>
   </sheetData>
